--- a/ПР3/Расчет Ceph и Garage.xlsx
+++ b/ПР3/Расчет Ceph и Garage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Mirea\Системы хранения данных\ПР3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE872DCB-DCF7-46C0-A6A4-8DA041635502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52597624-6123-4014-938C-BD31A77143E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1D163754-1A64-4024-9199-3E66102FB26D}"/>
+    <workbookView xWindow="3948" yWindow="2640" windowWidth="23040" windowHeight="12120" xr2:uid="{1D163754-1A64-4024-9199-3E66102FB26D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A2F374-C93B-4E61-A356-0298E97EE6DC}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -571,6 +571,18 @@
         <v>50787688</v>
       </c>
     </row>
+    <row r="18" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O18">
+        <f>L13/K13</f>
+        <v>3.6698457607855279</v>
+      </c>
+    </row>
+    <row r="19" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O19">
+        <f>L14/K14</f>
+        <v>18.218569653418889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
